--- a/data/trans_camb/IP08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 25,56</t>
+          <t>3,13; 25,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 10,2</t>
+          <t>-8,55; 10,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 30,23</t>
+          <t>-4,45; 28,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 20,48</t>
+          <t>-3,26; 21,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 5,84</t>
+          <t>-16,06; 5,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 9,51</t>
+          <t>-12,79; 10,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 19,81</t>
+          <t>2,81; 20,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 5,03</t>
+          <t>-9,96; 5,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 14,56</t>
+          <t>-5,94; 13,88</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 388,23</t>
+          <t>19,34; 440,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,29; 173,31</t>
+          <t>-58,12; 178,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,13; 463,66</t>
+          <t>-37,49; 494,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 164,93</t>
+          <t>-13,86; 178,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,53; 51,45</t>
+          <t>-65,13; 48,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,13; 76,46</t>
+          <t>-53,46; 77,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 177,74</t>
+          <t>10,79; 168,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 46,49</t>
+          <t>-50,65; 48,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 133,04</t>
+          <t>-34,13; 118,52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 8,19</t>
+          <t>-4,7; 8,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,28; -1,37</t>
+          <t>-12,3; -1,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 2,65</t>
+          <t>-10,85; 1,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 6,26</t>
+          <t>-6,75; 6,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,31; -2,32</t>
+          <t>-13,72; -2,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 1,93</t>
+          <t>-9,71; 2,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 5,55</t>
+          <t>-4,1; 5,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -3,25</t>
+          <t>-11,27; -3,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 0,47</t>
+          <t>-8,69; 0,54</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,21; 120,9</t>
+          <t>-38,05; 142,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-90,07; -10,95</t>
+          <t>-88,14; -8,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,41; 39,85</t>
+          <t>-78,03; 29,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,0; 82,19</t>
+          <t>-46,18; 100,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,27; -19,57</t>
+          <t>-91,06; -23,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,77; 29,15</t>
+          <t>-68,82; 39,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 70,81</t>
+          <t>-32,12; 73,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,84; -36,49</t>
+          <t>-85,54; -39,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,33; 6,62</t>
+          <t>-65,97; 7,99</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 15,2</t>
+          <t>-2,48; 14,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 6,96</t>
+          <t>-8,22; 7,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 13,04</t>
+          <t>-3,37; 13,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 9,88</t>
+          <t>-5,64; 8,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 3,14</t>
+          <t>-9,77; 2,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 13,92</t>
+          <t>-1,79; 14,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 9,75</t>
+          <t>-2,05; 9,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 3,44</t>
+          <t>-7,14; 2,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 11,39</t>
+          <t>-0,38; 11,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 381,74</t>
+          <t>-28,31; 336,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,93; 204,48</t>
+          <t>-73,66; 197,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,09; 360,09</t>
+          <t>-36,72; 363,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 263,95</t>
+          <t>-56,08; 233,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,38; 116,32</t>
+          <t>-90,59; 89,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 337,24</t>
+          <t>-23,33; 425,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 202,36</t>
+          <t>-23,5; 192,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-67,32; 79,05</t>
+          <t>-71,97; 61,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 219,84</t>
+          <t>-9,16; 235,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 2,77</t>
+          <t>-9,64; 3,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 10,84</t>
+          <t>-4,53; 10,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 13,61</t>
+          <t>-3,91; 14,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 8,28</t>
+          <t>-7,47; 8,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 10,84</t>
+          <t>-5,79; 9,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 50,32</t>
+          <t>3,43; 48,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 3,91</t>
+          <t>-6,82; 3,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 8,01</t>
+          <t>-2,33; 8,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 31,2</t>
+          <t>2,63; 31,87</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-79,34; 70,53</t>
+          <t>-80,52; 76,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 199,71</t>
+          <t>-39,82; 194,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 271,76</t>
+          <t>-40,05; 284,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 131,57</t>
+          <t>-60,42; 147,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 188,42</t>
+          <t>-46,46; 165,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,09; 955,12</t>
+          <t>17,1; 792,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,34; 69,25</t>
+          <t>-59,46; 51,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 123,45</t>
+          <t>-22,27; 134,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,24; 434,57</t>
+          <t>17,24; 417,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 13,16</t>
+          <t>-13,24; 10,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,55; -3,31</t>
+          <t>-22,96; -3,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 8,12</t>
+          <t>-15,14; 7,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 21,83</t>
+          <t>-3,4; 21,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,39; -0,58</t>
+          <t>-17,85; -0,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 10,18</t>
+          <t>-11,39; 10,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 12,71</t>
+          <t>-3,63; 12,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,01; -3,84</t>
+          <t>-15,91; -3,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 5,51</t>
+          <t>-9,63; 6,17</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-70,58; 239,0</t>
+          <t>-72,31; 169,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 22,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-76,0; 143,13</t>
+          <t>-80,03; 134,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 417,21</t>
+          <t>-24,99; 363,47</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 34,58</t>
+          <t>-100,0; 41,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 227,4</t>
+          <t>-68,57; 193,57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 169,47</t>
+          <t>-26,33; 145,33</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-95,78; -42,31</t>
+          <t>-95,46; -33,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 76,3</t>
+          <t>-63,56; 94,61</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,1; 15,85</t>
+          <t>-0,91; 15,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,62; 18,38</t>
+          <t>2,19; 18,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 13,43</t>
+          <t>-1,45; 13,37</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 16,69</t>
+          <t>-1,88; 16,8</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 15,62</t>
+          <t>-4,0; 15,82</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,2; 23,38</t>
+          <t>2,66; 22,76</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,78; 12,97</t>
+          <t>0,12; 12,68</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,71; 14,37</t>
+          <t>1,5; 14,52</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,91; 15,73</t>
+          <t>3,27; 15,77</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 1120,43</t>
+          <t>-52,38; 1379,51</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1316,23</t>
+          <t>-5,68; 1552,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 1013,39</t>
+          <t>-54,14; 972,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 422,2</t>
+          <t>-22,46; 405,77</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 375,59</t>
+          <t>-36,72; 330,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,33; 559,23</t>
+          <t>15,42; 568,45</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,05; 331,6</t>
+          <t>-0,58; 336,66</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>11,46; 388,33</t>
+          <t>9,17; 379,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>22,71; 384,26</t>
+          <t>29,86; 435,09</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 8,31</t>
+          <t>-3,81; 7,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,13</t>
+          <t>-7,5; 2,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 6,74</t>
+          <t>-4,88; 5,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 6,57</t>
+          <t>-5,1; 7,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 0,63</t>
+          <t>-10,39; 0,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 10,56</t>
+          <t>-3,4; 9,97</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,67</t>
+          <t>-2,85; 5,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 0,63</t>
+          <t>-7,5; 0,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 6,92</t>
+          <t>-2,49; 6,87</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 162,85</t>
+          <t>-39,33; 142,15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,72; 75,93</t>
+          <t>-71,36; 48,98</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-43,56; 142,92</t>
+          <t>-47,47; 113,68</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 79,86</t>
+          <t>-36,6; 94,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-69,52; 10,68</t>
+          <t>-72,73; 11,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 122,15</t>
+          <t>-25,54; 128,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 73,13</t>
+          <t>-24,4; 75,71</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 11,16</t>
+          <t>-63,38; 4,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 101,23</t>
+          <t>-21,53; 94,89</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 9,31</t>
+          <t>-1,05; 9,18</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 1,38</t>
+          <t>-6,85; 1,86</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 3,79</t>
+          <t>-6,11; 3,76</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 4,99</t>
+          <t>-6,58; 5,45</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -4,38</t>
+          <t>-14,07; -4,44</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,29; -3,62</t>
+          <t>-14,22; -3,82</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 5,4</t>
+          <t>-2,59; 5,87</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,36; -2,66</t>
+          <t>-8,96; -2,55</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -1,3</t>
+          <t>-8,7; -1,35</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 193,13</t>
+          <t>-13,37; 179,09</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 31,04</t>
+          <t>-67,77; 42,21</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,99; 73,16</t>
+          <t>-62,36; 77,34</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 48,4</t>
+          <t>-39,67; 48,32</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-81,44; -35,62</t>
+          <t>-82,53; -35,26</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-81,47; -25,59</t>
+          <t>-81,54; -29,43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 60,99</t>
+          <t>-20,61; 70,95</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-71,65; -28,54</t>
+          <t>-72,25; -29,32</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-65,92; -11,22</t>
+          <t>-67,92; -14,37</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,9</t>
+          <t>0,93; 6,05</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,7</t>
+          <t>-3,62; 0,66</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,45</t>
+          <t>-1,48; 4,77</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,83</t>
+          <t>-0,76; 5,0</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -2,31</t>
+          <t>-7,1; -2,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 6,05</t>
+          <t>-1,39; 5,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,58</t>
+          <t>0,74; 4,53</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,78; -1,51</t>
+          <t>-4,89; -1,46</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,08</t>
+          <t>-0,72; 4,53</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7,67; 84,63</t>
+          <t>9,58; 87,15</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 10,26</t>
+          <t>-39,5; 9,05</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 63,12</t>
+          <t>-16,58; 67,62</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 46,35</t>
+          <t>-5,06; 48,68</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-55,47; -21,96</t>
+          <t>-54,14; -21,59</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 59,46</t>
+          <t>-11,42; 59,36</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,16; 50,84</t>
+          <t>6,88; 50,18</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-43,99; -16,51</t>
+          <t>-44,57; -15,93</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 43,31</t>
+          <t>-7,46; 45,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 25,28</t>
+          <t>3,49; 26,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 10,8</t>
+          <t>-8,21; 10,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 28,23</t>
+          <t>-4,48; 28,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 21,41</t>
+          <t>-3,85; 22,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 5,9</t>
+          <t>-17,14; 5,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 10,18</t>
+          <t>-12,55; 10,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 20,0</t>
+          <t>2,04; 19,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 5,26</t>
+          <t>-9,54; 5,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 13,88</t>
+          <t>-6,16; 13,21</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,34; 440,46</t>
+          <t>8,12; 402,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-58,12; 178,17</t>
+          <t>-57,1; 171,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,49; 494,78</t>
+          <t>-39,56; 476,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 178,74</t>
+          <t>-15,94; 181,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,13; 48,33</t>
+          <t>-67,19; 51,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,46; 77,38</t>
+          <t>-53,45; 82,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,79; 168,95</t>
+          <t>9,67; 181,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,65; 48,44</t>
+          <t>-51,1; 46,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 118,52</t>
+          <t>-35,31; 119,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 8,83</t>
+          <t>-5,16; 8,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,3; -1,25</t>
+          <t>-12,99; -1,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 1,86</t>
+          <t>-10,44; 2,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 6,84</t>
+          <t>-7,21; 6,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,72; -2,45</t>
+          <t>-13,53; -2,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 2,73</t>
+          <t>-10,14; 2,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 5,7</t>
+          <t>-4,43; 4,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,27; -3,29</t>
+          <t>-11,02; -3,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 0,54</t>
+          <t>-8,81; 0,14</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,05; 142,01</t>
+          <t>-42,29; 142,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-88,14; -8,28</t>
+          <t>-89,46; -9,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,03; 29,3</t>
+          <t>-77,61; 39,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,18; 100,77</t>
+          <t>-50,4; 96,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,06; -23,78</t>
+          <t>-91,43; -26,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,82; 39,92</t>
+          <t>-71,39; 32,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 73,11</t>
+          <t>-33,65; 61,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,54; -39,14</t>
+          <t>-83,19; -37,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 7,99</t>
+          <t>-66,5; 4,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 14,47</t>
+          <t>-2,41; 14,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 7,14</t>
+          <t>-7,91; 7,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 13,68</t>
+          <t>-3,94; 13,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 8,82</t>
+          <t>-5,56; 8,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 2,52</t>
+          <t>-8,9; 3,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 14,84</t>
+          <t>-2,5; 14,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 9,43</t>
+          <t>-2,81; 8,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 2,61</t>
+          <t>-6,9; 2,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 11,53</t>
+          <t>-0,6; 11,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 336,91</t>
+          <t>-25,56; 379,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,66; 197,89</t>
+          <t>-74,02; 188,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,72; 363,4</t>
+          <t>-43,03; 330,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,08; 233,59</t>
+          <t>-59,31; 219,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,59; 89,25</t>
+          <t>-88,31; 111,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 425,99</t>
+          <t>-33,74; 370,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 192,63</t>
+          <t>-31,66; 164,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,97; 61,21</t>
+          <t>-68,98; 67,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 235,28</t>
+          <t>-9,34; 238,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 3,39</t>
+          <t>-10,2; 3,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 10,85</t>
+          <t>-4,79; 11,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 14,88</t>
+          <t>-4,36; 13,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 8,03</t>
+          <t>-7,71; 8,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 9,71</t>
+          <t>-6,1; 11,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 48,38</t>
+          <t>2,58; 48,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 3,49</t>
+          <t>-7,01; 3,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 8,74</t>
+          <t>-2,88; 8,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 31,87</t>
+          <t>2,9; 32,51</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 76,73</t>
+          <t>-81,36; 81,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 194,51</t>
+          <t>-42,33; 227,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,05; 284,45</t>
+          <t>-43,55; 237,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 147,03</t>
+          <t>-61,36; 152,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,46; 165,85</t>
+          <t>-51,67; 185,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,1; 792,47</t>
+          <t>24,3; 919,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-59,46; 51,55</t>
+          <t>-62,14; 44,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 134,52</t>
+          <t>-26,62; 120,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,24; 417,86</t>
+          <t>19,09; 434,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 10,77</t>
+          <t>-13,0; 11,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,96; -3,8</t>
+          <t>-21,04; -3,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 7,07</t>
+          <t>-15,22; 7,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 21,04</t>
+          <t>-2,24; 21,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,85; -0,55</t>
+          <t>-17,46; -0,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 10,18</t>
+          <t>-11,47; 9,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 12,49</t>
+          <t>-3,74; 13,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,91; -3,54</t>
+          <t>-16,26; -4,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 6,17</t>
+          <t>-9,61; 5,82</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 169,82</t>
+          <t>-71,88; 201,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,03; 134,56</t>
+          <t>-79,84; 140,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 363,47</t>
+          <t>-17,52; 404,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 41,0</t>
+          <t>-100,0; 48,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,57; 193,57</t>
+          <t>-73,33; 171,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 145,33</t>
+          <t>-28,0; 181,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-95,46; -33,77</t>
+          <t>-95,67; -41,26</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-63,56; 94,61</t>
+          <t>-59,76; 83,47</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 15,43</t>
+          <t>0,03; 14,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,19; 18,82</t>
+          <t>1,11; 18,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 13,37</t>
+          <t>-1,96; 14,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 16,8</t>
+          <t>-2,47; 16,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 15,82</t>
+          <t>-3,54; 16,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,66; 22,76</t>
+          <t>1,67; 22,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,12; 12,68</t>
+          <t>1,17; 13,63</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,5; 14,52</t>
+          <t>1,4; 14,56</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,27; 15,77</t>
+          <t>3,02; 15,79</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 1379,51</t>
+          <t>-32,4; 1063,01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 1552,49</t>
+          <t>-22,01; 1231,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 972,74</t>
+          <t>-59,95; 1148,79</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 405,77</t>
+          <t>-26,43; 360,2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-36,72; 330,2</t>
+          <t>-36,9; 338,86</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,42; 568,45</t>
+          <t>4,39; 491,28</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 336,66</t>
+          <t>1,23; 332,89</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9,17; 379,25</t>
+          <t>11,09; 415,31</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29,86; 435,09</t>
+          <t>27,72; 413,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 7,34</t>
+          <t>-4,23; 7,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 2,1</t>
+          <t>-7,63; 2,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 5,97</t>
+          <t>-4,43; 7,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 7,21</t>
+          <t>-4,74; 7,8</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 0,55</t>
+          <t>-10,03; 0,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 9,97</t>
+          <t>-3,53; 9,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 5,24</t>
+          <t>-3,15; 5,29</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,18</t>
+          <t>-7,49; 0,01</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 6,87</t>
+          <t>-2,15; 7,22</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 142,15</t>
+          <t>-42,38; 153,5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-71,36; 48,98</t>
+          <t>-69,86; 68,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 113,68</t>
+          <t>-46,07; 157,75</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 94,65</t>
+          <t>-37,16; 96,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 11,58</t>
+          <t>-69,76; 12,46</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 128,16</t>
+          <t>-25,34; 119,8</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,4; 75,71</t>
+          <t>-26,89; 72,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-63,38; 4,6</t>
+          <t>-64,96; 0,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 94,89</t>
+          <t>-21,64; 95,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,18</t>
+          <t>-0,88; 9,56</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 1,86</t>
+          <t>-6,68; 2,15</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 3,76</t>
+          <t>-5,52; 4,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 5,45</t>
+          <t>-6,6; 4,92</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-14,07; -4,44</t>
+          <t>-14,39; -4,12</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,22; -3,82</t>
+          <t>-14,17; -3,63</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 5,87</t>
+          <t>-2,43; 5,47</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -2,55</t>
+          <t>-9,21; -2,81</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,7; -1,35</t>
+          <t>-8,78; -1,59</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 179,09</t>
+          <t>-11,88; 194,03</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-67,77; 42,21</t>
+          <t>-68,14; 49,54</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,36; 77,34</t>
+          <t>-58,14; 84,91</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-39,67; 48,32</t>
+          <t>-39,68; 45,18</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-82,53; -35,26</t>
+          <t>-81,77; -34,41</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-81,54; -29,43</t>
+          <t>-83,0; -28,17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 70,95</t>
+          <t>-19,2; 62,31</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-72,25; -29,32</t>
+          <t>-72,39; -30,61</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-67,92; -14,37</t>
+          <t>-66,89; -16,16</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,05</t>
+          <t>0,9; 6,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,66</t>
+          <t>-3,91; 0,94</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,77</t>
+          <t>-1,19; 4,81</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,0</t>
+          <t>-0,64; 4,95</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -2,24</t>
+          <t>-7,08; -2,1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,94</t>
+          <t>-1,62; 6,36</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,53</t>
+          <t>0,69; 4,45</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -1,46</t>
+          <t>-4,79; -1,5</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,53</t>
+          <t>-0,62; 4,24</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>9,58; 87,15</t>
+          <t>9,76; 87,89</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 9,05</t>
+          <t>-40,35; 14,23</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 67,62</t>
+          <t>-13,79; 67,04</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 48,68</t>
+          <t>-5,96; 47,31</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -21,59</t>
+          <t>-54,82; -20,42</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 59,36</t>
+          <t>-13,35; 61,31</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,88; 50,18</t>
+          <t>6,14; 48,39</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-44,57; -15,93</t>
+          <t>-44,41; -16,04</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 45,97</t>
+          <t>-6,39; 43,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,91</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>14,45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,25</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,97</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,73</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,91</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,57</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>0,75</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 26,98</t>
+          <t>-4,29; 20,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 10,99</t>
+          <t>-15,19; 5,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 28,71</t>
+          <t>-11,62; 10,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 22,26</t>
+          <t>2,43; 25,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 5,72</t>
+          <t>-8,37; 10,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 10,11</t>
+          <t>-6,84; 13,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 19,92</t>
+          <t>1,4; 19,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 5,49</t>
+          <t>-9,93; 5,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 13,21</t>
+          <t>-6,71; 8,81</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>46,3%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-26,03%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-4,49%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>130,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>11,28%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>62,91%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46,3%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-26,03%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-8,35%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 402,21</t>
+          <t>-16,51; 164,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,1; 171,66</t>
+          <t>-61,53; 51,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,56; 476,16</t>
+          <t>-50,25; 89,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 181,56</t>
+          <t>5,92; 388,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,19; 51,96</t>
+          <t>-55,29; 173,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 82,14</t>
+          <t>-47,44; 226,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 181,61</t>
+          <t>7,4; 177,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,1; 46,03</t>
+          <t>-48,87; 46,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 119,19</t>
+          <t>-35,28; 78,1</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-7,71</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,38</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-6,41</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,87</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-7,71</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,97</t>
+          <t>-2,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,93</t>
+          <t>-3,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 8,87</t>
+          <t>-6,81; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,99; -1,36</t>
+          <t>-13,31; -2,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 2,68</t>
+          <t>-10,68; 1,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 6,94</t>
+          <t>-5,71; 8,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,53; -2,9</t>
+          <t>-13,28; -1,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 2,07</t>
+          <t>-9,21; 4,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 4,95</t>
+          <t>-4,13; 5,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,02; -3,35</t>
+          <t>-10,95; -3,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 0,14</t>
+          <t>-7,52; 1,09</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-1,15%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-71,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-40,38%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-64,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-38,95%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,15%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-71,11%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-36,65%</t>
+          <t>-21,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-37,83%</t>
+          <t>-31,78%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 142,3</t>
+          <t>-50,0; 82,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-89,46; -9,8</t>
+          <t>-90,27; -19,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,61; 39,51</t>
+          <t>-74,31; 26,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,4; 96,13</t>
+          <t>-45,21; 120,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,43; -26,4</t>
+          <t>-90,07; -10,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,39; 32,34</t>
+          <t>-66,7; 70,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 61,2</t>
+          <t>-33,78; 70,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,19; -37,02</t>
+          <t>-84,84; -36,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,5; 4,88</t>
+          <t>-60,7; 14,73</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,47</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,3</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,14</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,61</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,79</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,3</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>4,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 14,3</t>
+          <t>-5,11; 9,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 7,14</t>
+          <t>-8,94; 3,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 13,53</t>
+          <t>-3,35; 13,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 8,73</t>
+          <t>-2,91; 15,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 3,21</t>
+          <t>-7,87; 6,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 14,77</t>
+          <t>-4,79; 12,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 8,84</t>
+          <t>-1,9; 9,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 2,77</t>
+          <t>-6,61; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 11,31</t>
+          <t>-1,23; 10,64</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-45,96%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>71,62%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>79,13%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-8,03%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>63,17%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-45,96%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,56; 379,18</t>
+          <t>-55,75; 263,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,02; 188,35</t>
+          <t>-88,38; 116,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,03; 330,74</t>
+          <t>-34,18; 314,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,31; 219,64</t>
+          <t>-32,91; 381,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,31; 111,36</t>
+          <t>-74,93; 204,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 370,32</t>
+          <t>-43,17; 330,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 164,43</t>
+          <t>-21,12; 202,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,98; 67,88</t>
+          <t>-67,32; 79,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 238,19</t>
+          <t>-13,68; 214,02</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,33</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17,44</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-3,41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,03</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,41</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,96</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12,09</t>
+          <t>11,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 3,33</t>
+          <t>-7,8; 8,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 11,32</t>
+          <t>-5,87; 10,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 13,38</t>
+          <t>2,26; 46,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 8,61</t>
+          <t>-10,22; 2,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 11,24</t>
+          <t>-4,32; 10,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 48,25</t>
+          <t>-2,96; 15,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,09</t>
+          <t>-6,58; 3,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 8,16</t>
+          <t>-3,55; 8,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 32,51</t>
+          <t>3,16; 27,54</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-0,22%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24,67%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>184,55%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-38,59%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>34,29%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>49,92%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-0,22%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>24,67%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>200,63%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>132,09%</t>
+          <t>125,7%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-81,36; 81,14</t>
+          <t>-61,17; 131,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 227,14</t>
+          <t>-44,09; 188,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,55; 237,34</t>
+          <t>7,79; 838,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-61,36; 152,45</t>
+          <t>-79,34; 70,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 185,95</t>
+          <t>-36,87; 199,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,3; 919,09</t>
+          <t>-28,03; 293,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-62,14; 44,57</t>
+          <t>-57,34; 69,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 120,52</t>
+          <t>-30,67; 123,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,09; 434,92</t>
+          <t>18,68; 385,36</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>8,68</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-8,17</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,32</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-11,12</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,24</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8,68</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-8,17</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-3,13</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-1,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 11,02</t>
+          <t>-2,25; 21,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,04; -3,09</t>
+          <t>-17,39; -0,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 7,44</t>
+          <t>-10,71; 10,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 21,22</t>
+          <t>-12,71; 13,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,46; -0,66</t>
+          <t>-21,55; -3,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 9,81</t>
+          <t>-14,02; 8,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 13,3</t>
+          <t>-3,86; 12,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,26; -4,37</t>
+          <t>-16,01; -3,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 5,82</t>
+          <t>-9,16; 5,79</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>79,64%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-75,01%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-4,11%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-2,52%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-88,86%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-25,91%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>79,64%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-75,01%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-6,42%</t>
+          <t>-25,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-16,31%</t>
+          <t>-14,84%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 201,22</t>
+          <t>-17,94; 417,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 34,58</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>-70,15; 226,58</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-70,58; 239,0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>-79,84; 140,47</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>-17,52; 404,45</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 48,5</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-73,33; 171,13</t>
+          <t>-76,03; 147,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 181,54</t>
+          <t>-25,29; 169,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-95,67; -41,26</t>
+          <t>-95,78; -42,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 83,47</t>
+          <t>-59,52; 78,47</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>6,65</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5,58</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11,23</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>6,69</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>9,86</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>5,35</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>6,65</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>5,58</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,16</t>
+          <t>6,08</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,24</t>
+          <t>8,75</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,03; 14,64</t>
+          <t>-2,28; 16,69</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,11; 18,06</t>
+          <t>-3,72; 15,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 14,1</t>
+          <t>2,32; 22,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 16,43</t>
+          <t>0,1; 15,85</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 16,46</t>
+          <t>1,62; 18,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,67; 22,11</t>
+          <t>-0,72; 14,89</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,17; 13,63</t>
+          <t>0,78; 12,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,4; 14,56</t>
+          <t>1,71; 14,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,02; 15,79</t>
+          <t>2,23; 15,2</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>79,14%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>66,4%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>133,79%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>180,68%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>266,26%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>144,53%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>79,14%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>66,4%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>144,78%</t>
+          <t>164,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>150,91%</t>
+          <t>142,84%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 1063,01</t>
+          <t>-22,43; 422,2</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 1231,49</t>
+          <t>-36,52; 375,59</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 1148,79</t>
+          <t>10,3; 534,03</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 360,2</t>
+          <t>-49,42; 1120,43</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 338,86</t>
+          <t>-0,31; 1316,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,39; 491,28</t>
+          <t>-37,96; 1076,14</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,23; 332,89</t>
+          <t>2,05; 331,6</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>11,09; 415,31</t>
+          <t>11,46; 388,33</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>27,72; 413,05</t>
+          <t>20,65; 379,22</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-4,69</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3,89</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,74</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,23</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-4,69</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>2,67</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 7,11</t>
+          <t>-5,2; 6,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,67</t>
+          <t>-9,91; 0,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 7,02</t>
+          <t>-2,57; 10,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 7,8</t>
+          <t>-3,2; 8,31</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 0,78</t>
+          <t>-7,32; 3,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 9,96</t>
+          <t>-3,93; 7,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,29</t>
+          <t>-2,52; 5,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 0,01</t>
+          <t>-7,1; 0,63</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 7,22</t>
+          <t>-2,25; 7,18</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-42,25%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>35,04%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>22,86%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-29,26%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-42,25%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 153,5</t>
+          <t>-35,63; 79,86</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 68,57</t>
+          <t>-69,52; 10,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 157,75</t>
+          <t>-20,28; 130,93</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 96,88</t>
+          <t>-33,23; 162,85</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-69,76; 12,46</t>
+          <t>-69,72; 75,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 119,8</t>
+          <t>-41,55; 154,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 72,01</t>
+          <t>-23,57; 73,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-64,96; 0,08</t>
+          <t>-62,71; 11,16</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 95,11</t>
+          <t>-19,07; 104,01</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,76</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-9,09</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-8,73</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>4,05</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-2,44</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-9,09</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-8,81</t>
+          <t>-1,38</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-4,98</t>
+          <t>-5,13</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 9,56</t>
+          <t>-6,68; 4,99</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,15</t>
+          <t>-14,14; -4,38</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 4,0</t>
+          <t>-14,2; -3,5</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 4,92</t>
+          <t>-0,9; 9,31</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -4,12</t>
+          <t>-6,74; 1,38</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,17; -3,63</t>
+          <t>-6,63; 3,33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 5,47</t>
+          <t>-2,47; 5,4</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,21; -2,81</t>
+          <t>-9,36; -2,66</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,78; -1,59</t>
+          <t>-8,4; -1,39</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-5,42%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-65,0%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-62,43%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>55,61%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-33,53%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-12,79%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-5,42%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-65,0%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-62,97%</t>
+          <t>-18,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-46,54%</t>
+          <t>-47,99%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 194,03</t>
+          <t>-40,23; 48,4</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-68,14; 49,54</t>
+          <t>-81,44; -35,62</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 84,91</t>
+          <t>-81,33; -24,15</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-39,68; 45,18</t>
+          <t>-14,27; 193,13</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-81,77; -34,41</t>
+          <t>-67,71; 31,04</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-83,0; -28,17</t>
+          <t>-65,21; 68,55</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 62,31</t>
+          <t>-19,5; 60,99</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-72,39; -30,61</t>
+          <t>-71,65; -28,54</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-66,89; -16,16</t>
+          <t>-67,45; -13,27</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>2,03</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-4,63</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-1,47</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-4,63</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,03</t>
+          <t>-0,72; 4,83</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,94</t>
+          <t>-7,22; -2,31</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,81</t>
+          <t>-2,02; 5,33</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,95</t>
+          <t>0,79; 5,9</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -2,1</t>
+          <t>-3,9; 0,7</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 6,36</t>
+          <t>-1,33; 3,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,45</t>
+          <t>1,01; 4,58</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,79; -1,5</t>
+          <t>-4,78; -1,51</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,24</t>
+          <t>-1,17; 3,5</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-40,01%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>41,2%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-17,84%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-40,01%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>9,76; 87,89</t>
+          <t>-6,27; 46,35</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 14,23</t>
+          <t>-55,47; -21,96</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 67,04</t>
+          <t>-16,67; 52,75</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 47,31</t>
+          <t>7,67; 84,63</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-54,82; -20,42</t>
+          <t>-40,67; 10,26</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 61,31</t>
+          <t>-15,43; 55,19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,14; 48,39</t>
+          <t>9,16; 50,84</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-44,41; -16,04</t>
+          <t>-43,99; -16,51</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 43,93</t>
+          <t>-11,15; 37,9</t>
         </is>
       </c>
     </row>
